--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2010/KENTUCKY_2010.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2010/KENTUCKY_2010.xlsx
@@ -2526,7 +2526,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C121">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C382">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>Altzayanca</t>
+          <t>Atltzayanca</t>
         </is>
       </c>
       <c r="C550">
@@ -12084,7 +12084,7 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C652">
